--- a/templates/RUS_2025.xlsx
+++ b/templates/RUS_2025.xlsx
@@ -31,9 +31,6 @@
     <t>Причина увольнения</t>
   </si>
   <si>
-    <t>Степень родства</t>
-  </si>
-  <si>
     <t>Название учебного заведения и его местонахождение</t>
   </si>
   <si>
@@ -167,6 +164,9 @@
   </si>
   <si>
     <t>Являетесь ли Вы военнообязанным (воинское звание, место постановки на воинский учет)?</t>
+  </si>
+  <si>
+    <t>Степень родства и ФИО</t>
   </si>
 </sst>
 </file>
@@ -465,15 +465,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -483,100 +486,97 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -901,41 +901,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A1" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
+      <c r="A1" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
       <c r="O1" s="3"/>
     </row>
     <row r="2" spans="1:15" ht="15" customHeight="1" thickBot="1">
-      <c r="A2" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="A2" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
       <c r="K2" s="6"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="52"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="41"/>
     </row>
     <row r="3" spans="1:15" ht="15" customHeight="1" thickBot="1">
       <c r="A3" s="30"/>
@@ -949,47 +949,47 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
       <c r="K3" s="6"/>
-      <c r="L3" s="53"/>
+      <c r="L3" s="42"/>
       <c r="M3" s="31"/>
-      <c r="N3" s="54"/>
+      <c r="N3" s="43"/>
     </row>
     <row r="4" spans="1:15" ht="15" customHeight="1" thickBot="1">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="53"/>
+      <c r="L4" s="42"/>
       <c r="M4" s="31"/>
-      <c r="N4" s="54"/>
+      <c r="N4" s="43"/>
     </row>
     <row r="5" spans="1:15" ht="15" customHeight="1" thickBot="1">
       <c r="A5" s="31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" s="31"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
       <c r="K5" s="6"/>
-      <c r="L5" s="53"/>
+      <c r="L5" s="42"/>
       <c r="M5" s="31"/>
-      <c r="N5" s="54"/>
+      <c r="N5" s="43"/>
     </row>
     <row r="6" spans="1:15" ht="15" customHeight="1" thickBot="1">
       <c r="A6" s="31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="31"/>
       <c r="C6" s="30"/>
@@ -1001,13 +1001,13 @@
       <c r="I6" s="30"/>
       <c r="J6" s="30"/>
       <c r="K6" s="6"/>
-      <c r="L6" s="53"/>
+      <c r="L6" s="42"/>
       <c r="M6" s="31"/>
-      <c r="N6" s="54"/>
+      <c r="N6" s="43"/>
     </row>
     <row r="7" spans="1:15" ht="15" customHeight="1" thickBot="1">
       <c r="A7" s="31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="31"/>
       <c r="C7" s="30"/>
@@ -1017,49 +1017,49 @@
       <c r="G7" s="30"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30"/>
-      <c r="J7" s="50"/>
+      <c r="J7" s="39"/>
       <c r="K7" s="6"/>
-      <c r="L7" s="53"/>
+      <c r="L7" s="42"/>
       <c r="M7" s="31"/>
-      <c r="N7" s="54"/>
+      <c r="N7" s="43"/>
     </row>
     <row r="8" spans="1:15" ht="15" customHeight="1" thickBot="1">
-      <c r="A8" s="47"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47"/>
+      <c r="A8" s="46"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="46"/>
       <c r="K8" s="6"/>
-      <c r="L8" s="53"/>
+      <c r="L8" s="42"/>
       <c r="M8" s="31"/>
-      <c r="N8" s="54"/>
+      <c r="N8" s="43"/>
     </row>
     <row r="9" spans="1:15" ht="15" customHeight="1" thickBot="1">
-      <c r="A9" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
+      <c r="A9" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="32"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="33"/>
       <c r="K9" s="6"/>
-      <c r="L9" s="55"/>
+      <c r="L9" s="44"/>
       <c r="M9" s="30"/>
-      <c r="N9" s="56"/>
+      <c r="N9" s="45"/>
     </row>
     <row r="10" spans="1:15" ht="15" customHeight="1" thickBot="1">
       <c r="A10" s="31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="31"/>
       <c r="C10" s="31"/>
@@ -1077,7 +1077,7 @@
     </row>
     <row r="11" spans="1:15" ht="15" customHeight="1" thickBot="1">
       <c r="A11" s="31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" s="31"/>
       <c r="C11" s="31"/>
@@ -1086,16 +1086,16 @@
       <c r="F11" s="30"/>
       <c r="G11" s="30"/>
       <c r="H11" s="30"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="33"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="33"/>
     </row>
     <row r="12" spans="1:15" ht="15" customHeight="1" thickBot="1">
       <c r="A12" s="31" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B12" s="31"/>
       <c r="C12" s="31"/>
@@ -1103,13 +1103,13 @@
       <c r="E12" s="31"/>
       <c r="F12" s="31"/>
       <c r="G12" s="31"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="33"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="33"/>
     </row>
     <row r="13" spans="1:15" ht="15" customHeight="1" thickBot="1">
       <c r="A13" s="30"/>
@@ -1129,25 +1129,25 @@
     </row>
     <row r="14" spans="1:15" ht="15" customHeight="1" thickBot="1">
       <c r="A14" s="31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="31"/>
       <c r="C14" s="31"/>
       <c r="D14" s="31"/>
       <c r="E14" s="31"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="36"/>
-      <c r="L14" s="36"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="33"/>
     </row>
     <row r="15" spans="1:15" ht="15" customHeight="1" thickBot="1">
       <c r="A15" s="31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="31"/>
       <c r="C15" s="31"/>
@@ -1165,21 +1165,21 @@
     </row>
     <row r="16" spans="1:15" ht="15" customHeight="1" thickBot="1">
       <c r="A16" s="31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="31"/>
       <c r="C16" s="31"/>
       <c r="D16" s="31"/>
       <c r="E16" s="31"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="36"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="36"/>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
     </row>
     <row r="17" spans="1:15" ht="15" customHeight="1" thickBot="1">
       <c r="A17" s="31"/>
@@ -1187,15 +1187,15 @@
       <c r="C17" s="31"/>
       <c r="D17" s="31"/>
       <c r="E17" s="31"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="36"/>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="33"/>
     </row>
     <row r="18" spans="1:15" ht="15" customHeight="1" thickBot="1">
       <c r="A18" s="31"/>
@@ -1203,19 +1203,19 @@
       <c r="C18" s="31"/>
       <c r="D18" s="31"/>
       <c r="E18" s="31"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="36"/>
-      <c r="K18" s="36"/>
-      <c r="L18" s="36"/>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="33"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="33"/>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1" thickBot="1">
       <c r="A19" s="31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="31"/>
       <c r="C19" s="31"/>
@@ -1237,15 +1237,15 @@
       <c r="C20" s="31"/>
       <c r="D20" s="31"/>
       <c r="E20" s="31"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="36"/>
-      <c r="K20" s="36"/>
-      <c r="L20" s="36"/>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="33"/>
+      <c r="N20" s="33"/>
     </row>
     <row r="21" spans="1:15" ht="15" customHeight="1" thickBot="1">
       <c r="A21" s="31"/>
@@ -1253,184 +1253,184 @@
       <c r="C21" s="31"/>
       <c r="D21" s="31"/>
       <c r="E21" s="31"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
+      <c r="N21" s="33"/>
     </row>
     <row r="22" spans="1:15" s="1" customFormat="1" ht="25.05" customHeight="1" thickBot="1">
-      <c r="A22" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="48"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="48"/>
-      <c r="K22" s="48"/>
-      <c r="L22" s="48"/>
-      <c r="M22" s="48"/>
-      <c r="N22" s="48"/>
+      <c r="A22" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="51"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="51"/>
+      <c r="L22" s="51"/>
+      <c r="M22" s="51"/>
+      <c r="N22" s="51"/>
       <c r="O22" s="3"/>
     </row>
     <row r="23" spans="1:15" ht="124.05" customHeight="1" thickBot="1">
-      <c r="A23" s="23" t="s">
-        <v>4</v>
+      <c r="A23" s="24" t="s">
+        <v>3</v>
       </c>
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" s="24"/>
-      <c r="H23" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="I23" s="24"/>
-      <c r="J23" s="23" t="s">
-        <v>5</v>
+      <c r="E23" s="26"/>
+      <c r="F23" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="26"/>
+      <c r="H23" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="I23" s="26"/>
+      <c r="J23" s="24" t="s">
+        <v>4</v>
       </c>
       <c r="K23" s="25"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="N23" s="24"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="N23" s="26"/>
     </row>
     <row r="24" spans="1:15" ht="64.95" customHeight="1" thickBot="1">
       <c r="A24" s="21"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
       <c r="E24" s="22"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="45"/>
-      <c r="K24" s="47"/>
-      <c r="L24" s="46"/>
-      <c r="M24" s="45"/>
-      <c r="N24" s="46"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="49"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="50"/>
+      <c r="M24" s="49"/>
+      <c r="N24" s="50"/>
     </row>
     <row r="25" spans="1:15" ht="64.95" customHeight="1" thickBot="1">
       <c r="A25" s="21"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
       <c r="E25" s="22"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="26"/>
       <c r="H25" s="21"/>
       <c r="I25" s="22"/>
       <c r="J25" s="21"/>
-      <c r="K25" s="29"/>
+      <c r="K25" s="23"/>
       <c r="L25" s="22"/>
       <c r="M25" s="21"/>
       <c r="N25" s="22"/>
     </row>
     <row r="26" spans="1:15" ht="64.95" customHeight="1" thickBot="1">
       <c r="A26" s="21"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
       <c r="E26" s="22"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="26"/>
       <c r="H26" s="21"/>
       <c r="I26" s="22"/>
       <c r="J26" s="21"/>
-      <c r="K26" s="29"/>
+      <c r="K26" s="23"/>
       <c r="L26" s="22"/>
       <c r="M26" s="21"/>
       <c r="N26" s="22"/>
     </row>
     <row r="27" spans="1:15" ht="64.95" customHeight="1" thickBot="1">
       <c r="A27" s="21"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
       <c r="E27" s="22"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="26"/>
       <c r="H27" s="21"/>
       <c r="I27" s="22"/>
       <c r="J27" s="21"/>
-      <c r="K27" s="29"/>
+      <c r="K27" s="23"/>
       <c r="L27" s="22"/>
       <c r="M27" s="21"/>
       <c r="N27" s="22"/>
     </row>
     <row r="28" spans="1:15" ht="25.05" customHeight="1" thickBot="1">
-      <c r="A28" s="57" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="57"/>
-      <c r="C28" s="57"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="57"/>
-      <c r="K28" s="57"/>
-      <c r="L28" s="57"/>
-      <c r="M28" s="57"/>
-      <c r="N28" s="57"/>
+      <c r="A28" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
     </row>
     <row r="29" spans="1:15" s="6" customFormat="1" ht="85.05" customHeight="1" thickBot="1">
       <c r="A29" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B29" s="23" t="s">
-        <v>14</v>
+      <c r="B29" s="24" t="s">
+        <v>13</v>
       </c>
       <c r="C29" s="25"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="23" t="s">
-        <v>27</v>
+      <c r="D29" s="26"/>
+      <c r="E29" s="24" t="s">
+        <v>26</v>
       </c>
       <c r="F29" s="25"/>
-      <c r="G29" s="24"/>
+      <c r="G29" s="26"/>
       <c r="H29" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="I29" s="24"/>
-      <c r="J29" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="K29" s="59"/>
-      <c r="L29" s="60"/>
-      <c r="M29" s="23" t="s">
+      <c r="I29" s="26"/>
+      <c r="J29" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="K29" s="36"/>
+      <c r="L29" s="37"/>
+      <c r="M29" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="N29" s="24"/>
+      <c r="N29" s="26"/>
       <c r="O29" s="5"/>
     </row>
     <row r="30" spans="1:15" s="6" customFormat="1" ht="70.05" customHeight="1" thickBot="1">
       <c r="A30" s="2"/>
-      <c r="B30" s="26"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="23"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="24"/>
       <c r="F30" s="25"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="23"/>
-      <c r="I30" s="24"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="26"/>
       <c r="J30" s="21"/>
-      <c r="K30" s="29"/>
+      <c r="K30" s="23"/>
       <c r="L30" s="22"/>
       <c r="M30" s="21"/>
       <c r="N30" s="22"/>
@@ -1438,16 +1438,16 @@
     </row>
     <row r="31" spans="1:15" s="6" customFormat="1" ht="70.05" customHeight="1" thickBot="1">
       <c r="A31" s="2"/>
-      <c r="B31" s="26"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="23"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="24"/>
       <c r="F31" s="25"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="24"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="26"/>
       <c r="J31" s="21"/>
-      <c r="K31" s="29"/>
+      <c r="K31" s="23"/>
       <c r="L31" s="22"/>
       <c r="M31" s="21"/>
       <c r="N31" s="22"/>
@@ -1455,16 +1455,16 @@
     </row>
     <row r="32" spans="1:15" s="6" customFormat="1" ht="70.05" customHeight="1" thickBot="1">
       <c r="A32" s="2"/>
-      <c r="B32" s="26"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="23"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="24"/>
       <c r="F32" s="25"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="23"/>
-      <c r="I32" s="24"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="26"/>
       <c r="J32" s="21"/>
-      <c r="K32" s="29"/>
+      <c r="K32" s="23"/>
       <c r="L32" s="22"/>
       <c r="M32" s="21"/>
       <c r="N32" s="22"/>
@@ -1472,16 +1472,16 @@
     </row>
     <row r="33" spans="1:15" s="6" customFormat="1" ht="70.05" customHeight="1" thickBot="1">
       <c r="A33" s="2"/>
-      <c r="B33" s="26"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="23"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="24"/>
       <c r="F33" s="25"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="24"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="26"/>
       <c r="J33" s="21"/>
-      <c r="K33" s="29"/>
+      <c r="K33" s="23"/>
       <c r="L33" s="22"/>
       <c r="M33" s="21"/>
       <c r="N33" s="22"/>
@@ -1489,16 +1489,16 @@
     </row>
     <row r="34" spans="1:15" s="6" customFormat="1" ht="70.05" customHeight="1" thickBot="1">
       <c r="A34" s="2"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="23"/>
+      <c r="B34" s="27"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="24"/>
       <c r="F34" s="25"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="24"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="26"/>
       <c r="J34" s="21"/>
-      <c r="K34" s="29"/>
+      <c r="K34" s="23"/>
       <c r="L34" s="22"/>
       <c r="M34" s="21"/>
       <c r="N34" s="22"/>
@@ -1523,23 +1523,23 @@
     </row>
     <row r="36" spans="1:15" ht="73.8" customHeight="1" thickBot="1">
       <c r="A36" s="2"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="23"/>
+      <c r="B36" s="27"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="24"/>
       <c r="F36" s="25"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="23"/>
-      <c r="I36" s="24"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="26"/>
       <c r="J36" s="21"/>
-      <c r="K36" s="29"/>
+      <c r="K36" s="23"/>
       <c r="L36" s="22"/>
       <c r="M36" s="21"/>
       <c r="N36" s="22"/>
     </row>
     <row r="37" spans="1:15" ht="15" customHeight="1">
       <c r="A37" s="31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B37" s="31"/>
       <c r="C37" s="31"/>
@@ -1621,287 +1621,287 @@
     </row>
     <row r="42" spans="1:15" s="6" customFormat="1" ht="40.049999999999997" customHeight="1" thickBot="1">
       <c r="A42" s="30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" s="30"/>
       <c r="C42" s="30"/>
       <c r="D42" s="30"/>
       <c r="E42" s="30"/>
       <c r="F42" s="30"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="36"/>
-      <c r="I42" s="36"/>
-      <c r="J42" s="36"/>
-      <c r="K42" s="36"/>
-      <c r="L42" s="36"/>
-      <c r="M42" s="36"/>
-      <c r="N42" s="36"/>
+      <c r="G42" s="33"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="33"/>
+      <c r="J42" s="33"/>
+      <c r="K42" s="33"/>
+      <c r="L42" s="33"/>
+      <c r="M42" s="33"/>
+      <c r="N42" s="33"/>
       <c r="O42" s="5"/>
     </row>
     <row r="43" spans="1:15" s="6" customFormat="1" ht="40.049999999999997" customHeight="1" thickBot="1">
       <c r="A43" s="21"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="29"/>
-      <c r="M43" s="29"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
+      <c r="J43" s="23"/>
+      <c r="K43" s="23"/>
+      <c r="L43" s="23"/>
+      <c r="M43" s="23"/>
       <c r="N43" s="22"/>
       <c r="O43" s="5"/>
     </row>
     <row r="44" spans="1:15" s="6" customFormat="1" ht="40.049999999999997" customHeight="1" thickBot="1">
       <c r="A44" s="21"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="29"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="29"/>
-      <c r="H44" s="29"/>
-      <c r="I44" s="29"/>
-      <c r="J44" s="29"/>
-      <c r="K44" s="29"/>
-      <c r="L44" s="29"/>
-      <c r="M44" s="29"/>
+      <c r="B44" s="23"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="23"/>
+      <c r="I44" s="23"/>
+      <c r="J44" s="23"/>
+      <c r="K44" s="23"/>
+      <c r="L44" s="23"/>
+      <c r="M44" s="23"/>
       <c r="N44" s="22"/>
       <c r="O44" s="5"/>
     </row>
     <row r="45" spans="1:15" s="6" customFormat="1" ht="40.049999999999997" customHeight="1" thickBot="1">
       <c r="A45" s="21"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="29"/>
-      <c r="D45" s="29"/>
-      <c r="E45" s="29"/>
-      <c r="F45" s="29"/>
-      <c r="G45" s="29"/>
-      <c r="H45" s="29"/>
-      <c r="I45" s="29"/>
-      <c r="J45" s="29"/>
-      <c r="K45" s="29"/>
-      <c r="L45" s="29"/>
-      <c r="M45" s="29"/>
+      <c r="B45" s="23"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="23"/>
+      <c r="G45" s="23"/>
+      <c r="H45" s="23"/>
+      <c r="I45" s="23"/>
+      <c r="J45" s="23"/>
+      <c r="K45" s="23"/>
+      <c r="L45" s="23"/>
+      <c r="M45" s="23"/>
       <c r="N45" s="22"/>
       <c r="O45" s="5"/>
     </row>
     <row r="46" spans="1:15" ht="25.05" customHeight="1" thickBot="1">
       <c r="A46" s="21"/>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="23"/>
+      <c r="G46" s="23"/>
+      <c r="H46" s="23"/>
+      <c r="I46" s="23"/>
+      <c r="J46" s="23"/>
+      <c r="K46" s="23"/>
+      <c r="L46" s="23"/>
+      <c r="M46" s="23"/>
       <c r="N46" s="22"/>
     </row>
     <row r="47" spans="1:15" s="8" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A47" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="32"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="32"/>
-      <c r="E47" s="32"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32"/>
-      <c r="I47" s="32"/>
-      <c r="J47" s="32"/>
-      <c r="K47" s="32"/>
-      <c r="L47" s="32"/>
-      <c r="M47" s="32"/>
-      <c r="N47" s="32"/>
+      <c r="A47" s="60" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="60"/>
+      <c r="C47" s="60"/>
+      <c r="D47" s="60"/>
+      <c r="E47" s="60"/>
+      <c r="F47" s="60"/>
+      <c r="G47" s="60"/>
+      <c r="H47" s="60"/>
+      <c r="I47" s="60"/>
+      <c r="J47" s="60"/>
+      <c r="K47" s="60"/>
+      <c r="L47" s="60"/>
+      <c r="M47" s="60"/>
+      <c r="N47" s="60"/>
       <c r="O47" s="5"/>
     </row>
     <row r="48" spans="1:15" s="6" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A48" s="23" t="s">
-        <v>3</v>
+      <c r="A48" s="24" t="s">
+        <v>48</v>
       </c>
       <c r="B48" s="25"/>
-      <c r="C48" s="24"/>
+      <c r="C48" s="26"/>
       <c r="D48" s="25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E48" s="25"/>
-      <c r="F48" s="24"/>
-      <c r="G48" s="23" t="s">
-        <v>16</v>
+      <c r="F48" s="26"/>
+      <c r="G48" s="24" t="s">
+        <v>15</v>
       </c>
       <c r="H48" s="25"/>
       <c r="I48" s="25"/>
-      <c r="J48" s="24"/>
-      <c r="K48" s="23" t="s">
-        <v>15</v>
+      <c r="J48" s="26"/>
+      <c r="K48" s="24" t="s">
+        <v>14</v>
       </c>
       <c r="L48" s="25"/>
       <c r="M48" s="25"/>
-      <c r="N48" s="24"/>
+      <c r="N48" s="26"/>
       <c r="O48" s="5"/>
     </row>
     <row r="49" spans="1:15" s="6" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A49" s="23"/>
+      <c r="A49" s="24"/>
       <c r="B49" s="25"/>
-      <c r="C49" s="24"/>
+      <c r="C49" s="26"/>
       <c r="D49" s="25"/>
       <c r="E49" s="25"/>
-      <c r="F49" s="24"/>
-      <c r="G49" s="23"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="24"/>
       <c r="H49" s="25"/>
       <c r="I49" s="25"/>
-      <c r="J49" s="24"/>
+      <c r="J49" s="26"/>
       <c r="K49" s="21"/>
-      <c r="L49" s="29"/>
-      <c r="M49" s="29"/>
+      <c r="L49" s="23"/>
+      <c r="M49" s="23"/>
       <c r="N49" s="22"/>
       <c r="O49" s="5"/>
     </row>
     <row r="50" spans="1:15" s="6" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A50" s="23"/>
+      <c r="A50" s="24"/>
       <c r="B50" s="25"/>
-      <c r="C50" s="24"/>
+      <c r="C50" s="26"/>
       <c r="D50" s="25"/>
       <c r="E50" s="25"/>
-      <c r="F50" s="24"/>
-      <c r="G50" s="23"/>
+      <c r="F50" s="26"/>
+      <c r="G50" s="24"/>
       <c r="H50" s="25"/>
       <c r="I50" s="25"/>
-      <c r="J50" s="24"/>
+      <c r="J50" s="26"/>
       <c r="K50" s="21"/>
-      <c r="L50" s="29"/>
-      <c r="M50" s="29"/>
+      <c r="L50" s="23"/>
+      <c r="M50" s="23"/>
       <c r="N50" s="22"/>
       <c r="O50" s="5"/>
     </row>
     <row r="51" spans="1:15" s="6" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A51" s="23"/>
+      <c r="A51" s="24"/>
       <c r="B51" s="25"/>
-      <c r="C51" s="24"/>
+      <c r="C51" s="26"/>
       <c r="D51" s="25"/>
       <c r="E51" s="25"/>
-      <c r="F51" s="24"/>
-      <c r="G51" s="23"/>
+      <c r="F51" s="26"/>
+      <c r="G51" s="24"/>
       <c r="H51" s="25"/>
       <c r="I51" s="25"/>
-      <c r="J51" s="24"/>
+      <c r="J51" s="26"/>
       <c r="K51" s="21"/>
-      <c r="L51" s="29"/>
-      <c r="M51" s="29"/>
+      <c r="L51" s="23"/>
+      <c r="M51" s="23"/>
       <c r="N51" s="22"/>
       <c r="O51" s="5"/>
     </row>
     <row r="52" spans="1:15" s="6" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A52" s="23"/>
+      <c r="A52" s="24"/>
       <c r="B52" s="25"/>
-      <c r="C52" s="24"/>
+      <c r="C52" s="26"/>
       <c r="D52" s="25"/>
       <c r="E52" s="25"/>
-      <c r="F52" s="24"/>
-      <c r="G52" s="23"/>
+      <c r="F52" s="26"/>
+      <c r="G52" s="24"/>
       <c r="H52" s="25"/>
       <c r="I52" s="25"/>
-      <c r="J52" s="24"/>
+      <c r="J52" s="26"/>
       <c r="K52" s="21"/>
-      <c r="L52" s="29"/>
-      <c r="M52" s="29"/>
+      <c r="L52" s="23"/>
+      <c r="M52" s="23"/>
       <c r="N52" s="22"/>
       <c r="O52" s="5"/>
     </row>
     <row r="53" spans="1:15" s="6" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A53" s="23"/>
+      <c r="A53" s="24"/>
       <c r="B53" s="25"/>
-      <c r="C53" s="24"/>
+      <c r="C53" s="26"/>
       <c r="D53" s="25"/>
       <c r="E53" s="25"/>
-      <c r="F53" s="24"/>
-      <c r="G53" s="23"/>
+      <c r="F53" s="26"/>
+      <c r="G53" s="24"/>
       <c r="H53" s="25"/>
       <c r="I53" s="25"/>
-      <c r="J53" s="24"/>
+      <c r="J53" s="26"/>
       <c r="K53" s="21"/>
-      <c r="L53" s="29"/>
-      <c r="M53" s="29"/>
+      <c r="L53" s="23"/>
+      <c r="M53" s="23"/>
       <c r="N53" s="22"/>
       <c r="O53" s="5"/>
     </row>
     <row r="54" spans="1:15" s="6" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A54" s="23"/>
+      <c r="A54" s="24"/>
       <c r="B54" s="25"/>
-      <c r="C54" s="24"/>
+      <c r="C54" s="26"/>
       <c r="D54" s="25"/>
       <c r="E54" s="25"/>
-      <c r="F54" s="24"/>
-      <c r="G54" s="23"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="24"/>
       <c r="H54" s="25"/>
       <c r="I54" s="25"/>
-      <c r="J54" s="24"/>
+      <c r="J54" s="26"/>
       <c r="K54" s="21"/>
-      <c r="L54" s="29"/>
-      <c r="M54" s="29"/>
+      <c r="L54" s="23"/>
+      <c r="M54" s="23"/>
       <c r="N54" s="22"/>
       <c r="O54" s="5"/>
     </row>
     <row r="55" spans="1:15" s="6" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A55" s="23"/>
+      <c r="A55" s="24"/>
       <c r="B55" s="25"/>
-      <c r="C55" s="24"/>
+      <c r="C55" s="26"/>
       <c r="D55" s="25"/>
       <c r="E55" s="25"/>
-      <c r="F55" s="24"/>
-      <c r="G55" s="23"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="24"/>
       <c r="H55" s="25"/>
       <c r="I55" s="25"/>
-      <c r="J55" s="24"/>
+      <c r="J55" s="26"/>
       <c r="K55" s="21"/>
-      <c r="L55" s="29"/>
-      <c r="M55" s="29"/>
+      <c r="L55" s="23"/>
+      <c r="M55" s="23"/>
       <c r="N55" s="22"/>
       <c r="O55" s="5"/>
     </row>
     <row r="56" spans="1:15" s="6" customFormat="1" ht="25.05" customHeight="1" thickBot="1">
-      <c r="A56" s="23"/>
+      <c r="A56" s="24"/>
       <c r="B56" s="25"/>
-      <c r="C56" s="24"/>
+      <c r="C56" s="26"/>
       <c r="D56" s="25"/>
       <c r="E56" s="25"/>
-      <c r="F56" s="24"/>
-      <c r="G56" s="23"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="24"/>
       <c r="H56" s="25"/>
       <c r="I56" s="25"/>
-      <c r="J56" s="24"/>
+      <c r="J56" s="26"/>
       <c r="K56" s="21"/>
-      <c r="L56" s="29"/>
-      <c r="M56" s="29"/>
+      <c r="L56" s="23"/>
+      <c r="M56" s="23"/>
       <c r="N56" s="22"/>
       <c r="O56" s="5"/>
     </row>
     <row r="57" spans="1:15" ht="15" customHeight="1">
-      <c r="A57" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="B57" s="33"/>
-      <c r="C57" s="33"/>
-      <c r="D57" s="33"/>
-      <c r="E57" s="33"/>
-      <c r="F57" s="33"/>
-      <c r="G57" s="33"/>
-      <c r="H57" s="33"/>
-      <c r="I57" s="33"/>
-      <c r="J57" s="33"/>
-      <c r="K57" s="33"/>
-      <c r="L57" s="33"/>
-      <c r="M57" s="33"/>
-      <c r="N57" s="33"/>
+      <c r="A57" s="58" t="s">
+        <v>47</v>
+      </c>
+      <c r="B57" s="58"/>
+      <c r="C57" s="58"/>
+      <c r="D57" s="58"/>
+      <c r="E57" s="58"/>
+      <c r="F57" s="58"/>
+      <c r="G57" s="58"/>
+      <c r="H57" s="58"/>
+      <c r="I57" s="58"/>
+      <c r="J57" s="58"/>
+      <c r="K57" s="58"/>
+      <c r="L57" s="58"/>
+      <c r="M57" s="58"/>
+      <c r="N57" s="58"/>
     </row>
     <row r="58" spans="1:15" ht="15" customHeight="1" thickBot="1">
       <c r="A58" s="30"/>
@@ -1936,22 +1936,22 @@
       <c r="N59" s="30"/>
     </row>
     <row r="60" spans="1:15" ht="15" customHeight="1">
-      <c r="A60" s="44" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="44"/>
-      <c r="C60" s="44"/>
-      <c r="D60" s="44"/>
-      <c r="E60" s="44"/>
-      <c r="F60" s="44"/>
-      <c r="G60" s="44"/>
-      <c r="H60" s="44"/>
-      <c r="I60" s="44"/>
-      <c r="J60" s="44"/>
-      <c r="K60" s="44"/>
-      <c r="L60" s="44"/>
-      <c r="M60" s="44"/>
-      <c r="N60" s="44"/>
+      <c r="A60" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="B60" s="48"/>
+      <c r="C60" s="48"/>
+      <c r="D60" s="48"/>
+      <c r="E60" s="48"/>
+      <c r="F60" s="48"/>
+      <c r="G60" s="48"/>
+      <c r="H60" s="48"/>
+      <c r="I60" s="48"/>
+      <c r="J60" s="48"/>
+      <c r="K60" s="48"/>
+      <c r="L60" s="48"/>
+      <c r="M60" s="48"/>
+      <c r="N60" s="48"/>
     </row>
     <row r="61" spans="1:15" ht="15" customHeight="1" thickBot="1">
       <c r="A61" s="30"/>
@@ -1986,22 +1986,22 @@
       <c r="N62" s="30"/>
     </row>
     <row r="63" spans="1:15" ht="15" customHeight="1">
-      <c r="A63" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="B63" s="33"/>
-      <c r="C63" s="33"/>
-      <c r="D63" s="33"/>
-      <c r="E63" s="33"/>
-      <c r="F63" s="33"/>
-      <c r="G63" s="33"/>
-      <c r="H63" s="33"/>
-      <c r="I63" s="33"/>
-      <c r="J63" s="33"/>
-      <c r="K63" s="33"/>
-      <c r="L63" s="33"/>
-      <c r="M63" s="33"/>
-      <c r="N63" s="33"/>
+      <c r="A63" s="58" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="58"/>
+      <c r="C63" s="58"/>
+      <c r="D63" s="58"/>
+      <c r="E63" s="58"/>
+      <c r="F63" s="58"/>
+      <c r="G63" s="58"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="58"/>
+      <c r="K63" s="58"/>
+      <c r="L63" s="58"/>
+      <c r="M63" s="58"/>
+      <c r="N63" s="58"/>
     </row>
     <row r="64" spans="1:15" ht="15" customHeight="1" thickBot="1">
       <c r="A64" s="30"/>
@@ -2052,22 +2052,22 @@
       <c r="N66" s="30"/>
     </row>
     <row r="67" spans="1:14" ht="15" customHeight="1">
-      <c r="A67" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="B67" s="33"/>
-      <c r="C67" s="33"/>
-      <c r="D67" s="33"/>
-      <c r="E67" s="33"/>
-      <c r="F67" s="33"/>
-      <c r="G67" s="33"/>
-      <c r="H67" s="33"/>
-      <c r="I67" s="33"/>
-      <c r="J67" s="33"/>
-      <c r="K67" s="33"/>
-      <c r="L67" s="33"/>
-      <c r="M67" s="33"/>
-      <c r="N67" s="33"/>
+      <c r="A67" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="B67" s="58"/>
+      <c r="C67" s="58"/>
+      <c r="D67" s="58"/>
+      <c r="E67" s="58"/>
+      <c r="F67" s="58"/>
+      <c r="G67" s="58"/>
+      <c r="H67" s="58"/>
+      <c r="I67" s="58"/>
+      <c r="J67" s="58"/>
+      <c r="K67" s="58"/>
+      <c r="L67" s="58"/>
+      <c r="M67" s="58"/>
+      <c r="N67" s="58"/>
     </row>
     <row r="68" spans="1:14" ht="15" customHeight="1" thickBot="1">
       <c r="A68" s="30"/>
@@ -2118,28 +2118,28 @@
       <c r="N70" s="30"/>
     </row>
     <row r="71" spans="1:14" ht="15" customHeight="1" thickBot="1">
-      <c r="A71" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="B71" s="34"/>
-      <c r="C71" s="34"/>
-      <c r="D71" s="34"/>
-      <c r="E71" s="34"/>
-      <c r="F71" s="34"/>
-      <c r="G71" s="34"/>
-      <c r="H71" s="36"/>
-      <c r="I71" s="36"/>
-      <c r="J71" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="K71" s="35"/>
-      <c r="L71" s="35"/>
-      <c r="M71" s="36"/>
-      <c r="N71" s="36"/>
+      <c r="A71" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B71" s="32"/>
+      <c r="C71" s="32"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="33"/>
+      <c r="I71" s="33"/>
+      <c r="J71" s="59" t="s">
+        <v>30</v>
+      </c>
+      <c r="K71" s="59"/>
+      <c r="L71" s="59"/>
+      <c r="M71" s="33"/>
+      <c r="N71" s="33"/>
     </row>
     <row r="72" spans="1:14" ht="25.05" customHeight="1" thickBot="1">
       <c r="A72" s="31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B72" s="31"/>
       <c r="C72" s="31"/>
@@ -2157,21 +2157,21 @@
     </row>
     <row r="73" spans="1:14" ht="15" customHeight="1">
       <c r="A73" s="31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B73" s="31"/>
       <c r="C73" s="31"/>
       <c r="D73" s="31"/>
       <c r="E73" s="31"/>
-      <c r="F73" s="34"/>
-      <c r="G73" s="34"/>
-      <c r="H73" s="34"/>
-      <c r="I73" s="34"/>
-      <c r="J73" s="34"/>
-      <c r="K73" s="34"/>
-      <c r="L73" s="34"/>
-      <c r="M73" s="34"/>
-      <c r="N73" s="34"/>
+      <c r="F73" s="32"/>
+      <c r="G73" s="32"/>
+      <c r="H73" s="32"/>
+      <c r="I73" s="32"/>
+      <c r="J73" s="32"/>
+      <c r="K73" s="32"/>
+      <c r="L73" s="32"/>
+      <c r="M73" s="32"/>
+      <c r="N73" s="32"/>
     </row>
     <row r="74" spans="1:14" ht="25.05" customHeight="1" thickBot="1">
       <c r="A74" s="30"/>
@@ -2190,22 +2190,22 @@
       <c r="N74" s="30"/>
     </row>
     <row r="75" spans="1:14" ht="15" customHeight="1">
-      <c r="A75" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="B75" s="34"/>
-      <c r="C75" s="34"/>
-      <c r="D75" s="34"/>
-      <c r="E75" s="34"/>
-      <c r="F75" s="34"/>
-      <c r="G75" s="34"/>
-      <c r="H75" s="34"/>
-      <c r="I75" s="34"/>
-      <c r="J75" s="34"/>
-      <c r="K75" s="34"/>
-      <c r="L75" s="34"/>
-      <c r="M75" s="34"/>
-      <c r="N75" s="34"/>
+      <c r="A75" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B75" s="32"/>
+      <c r="C75" s="32"/>
+      <c r="D75" s="32"/>
+      <c r="E75" s="32"/>
+      <c r="F75" s="32"/>
+      <c r="G75" s="32"/>
+      <c r="H75" s="32"/>
+      <c r="I75" s="32"/>
+      <c r="J75" s="32"/>
+      <c r="K75" s="32"/>
+      <c r="L75" s="32"/>
+      <c r="M75" s="32"/>
+      <c r="N75" s="32"/>
     </row>
     <row r="76" spans="1:14" ht="25.05" customHeight="1" thickBot="1">
       <c r="A76" s="30"/>
@@ -2224,22 +2224,22 @@
       <c r="N76" s="30"/>
     </row>
     <row r="77" spans="1:14" ht="15" customHeight="1">
-      <c r="A77" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="B77" s="33"/>
-      <c r="C77" s="33"/>
-      <c r="D77" s="33"/>
-      <c r="E77" s="33"/>
-      <c r="F77" s="33"/>
-      <c r="G77" s="33"/>
-      <c r="H77" s="33"/>
-      <c r="I77" s="33"/>
-      <c r="J77" s="33"/>
-      <c r="K77" s="33"/>
-      <c r="L77" s="33"/>
-      <c r="M77" s="33"/>
-      <c r="N77" s="33"/>
+      <c r="A77" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="B77" s="58"/>
+      <c r="C77" s="58"/>
+      <c r="D77" s="58"/>
+      <c r="E77" s="58"/>
+      <c r="F77" s="58"/>
+      <c r="G77" s="58"/>
+      <c r="H77" s="58"/>
+      <c r="I77" s="58"/>
+      <c r="J77" s="58"/>
+      <c r="K77" s="58"/>
+      <c r="L77" s="58"/>
+      <c r="M77" s="58"/>
+      <c r="N77" s="58"/>
     </row>
     <row r="78" spans="1:14" ht="25.05" customHeight="1" thickBot="1">
       <c r="A78" s="30"/>
@@ -2259,7 +2259,7 @@
     </row>
     <row r="79" spans="1:14" ht="15" customHeight="1">
       <c r="A79" s="31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B79" s="31"/>
       <c r="C79" s="31"/>
@@ -2324,22 +2324,22 @@
       <c r="N82" s="30"/>
     </row>
     <row r="83" spans="1:15" ht="15" customHeight="1">
-      <c r="A83" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="B83" s="34"/>
-      <c r="C83" s="34"/>
-      <c r="D83" s="34"/>
-      <c r="E83" s="34"/>
-      <c r="F83" s="34"/>
-      <c r="G83" s="34"/>
-      <c r="H83" s="34"/>
-      <c r="I83" s="34"/>
-      <c r="J83" s="34"/>
-      <c r="K83" s="34"/>
-      <c r="L83" s="34"/>
-      <c r="M83" s="34"/>
-      <c r="N83" s="34"/>
+      <c r="A83" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B83" s="32"/>
+      <c r="C83" s="32"/>
+      <c r="D83" s="32"/>
+      <c r="E83" s="32"/>
+      <c r="F83" s="32"/>
+      <c r="G83" s="32"/>
+      <c r="H83" s="32"/>
+      <c r="I83" s="32"/>
+      <c r="J83" s="32"/>
+      <c r="K83" s="32"/>
+      <c r="L83" s="32"/>
+      <c r="M83" s="32"/>
+      <c r="N83" s="32"/>
     </row>
     <row r="84" spans="1:15" ht="15" customHeight="1" thickBot="1">
       <c r="A84" s="30"/>
@@ -2390,22 +2390,22 @@
       <c r="N86" s="30"/>
     </row>
     <row r="87" spans="1:15" ht="15" customHeight="1">
-      <c r="A87" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="B87" s="34"/>
-      <c r="C87" s="34"/>
-      <c r="D87" s="34"/>
-      <c r="E87" s="34"/>
-      <c r="F87" s="34"/>
-      <c r="G87" s="34"/>
-      <c r="H87" s="34"/>
-      <c r="I87" s="34"/>
-      <c r="J87" s="34"/>
-      <c r="K87" s="34"/>
-      <c r="L87" s="34"/>
-      <c r="M87" s="34"/>
-      <c r="N87" s="34"/>
+      <c r="A87" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B87" s="32"/>
+      <c r="C87" s="32"/>
+      <c r="D87" s="32"/>
+      <c r="E87" s="32"/>
+      <c r="F87" s="32"/>
+      <c r="G87" s="32"/>
+      <c r="H87" s="32"/>
+      <c r="I87" s="32"/>
+      <c r="J87" s="32"/>
+      <c r="K87" s="32"/>
+      <c r="L87" s="32"/>
+      <c r="M87" s="32"/>
+      <c r="N87" s="32"/>
     </row>
     <row r="88" spans="1:15" ht="15" customHeight="1" thickBot="1">
       <c r="A88" s="30"/>
@@ -2440,25 +2440,25 @@
       <c r="N89" s="30"/>
     </row>
     <row r="90" spans="1:15" s="6" customFormat="1" ht="25.05" customHeight="1" thickBot="1">
-      <c r="A90" s="36"/>
-      <c r="B90" s="36"/>
-      <c r="C90" s="36"/>
-      <c r="D90" s="36"/>
-      <c r="E90" s="36"/>
-      <c r="F90" s="36"/>
-      <c r="G90" s="36"/>
-      <c r="H90" s="36"/>
-      <c r="I90" s="36"/>
-      <c r="J90" s="36"/>
-      <c r="K90" s="36"/>
-      <c r="L90" s="36"/>
-      <c r="M90" s="36"/>
-      <c r="N90" s="36"/>
+      <c r="A90" s="33"/>
+      <c r="B90" s="33"/>
+      <c r="C90" s="33"/>
+      <c r="D90" s="33"/>
+      <c r="E90" s="33"/>
+      <c r="F90" s="33"/>
+      <c r="G90" s="33"/>
+      <c r="H90" s="33"/>
+      <c r="I90" s="33"/>
+      <c r="J90" s="33"/>
+      <c r="K90" s="33"/>
+      <c r="L90" s="33"/>
+      <c r="M90" s="33"/>
+      <c r="N90" s="33"/>
       <c r="O90" s="5"/>
     </row>
     <row r="91" spans="1:15" ht="15" customHeight="1">
       <c r="A91" s="31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B91" s="31"/>
       <c r="C91" s="31"/>
@@ -2475,92 +2475,92 @@
       <c r="N91" s="31"/>
     </row>
     <row r="92" spans="1:15" s="6" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A92" s="43"/>
-      <c r="B92" s="43"/>
-      <c r="C92" s="43"/>
-      <c r="D92" s="43"/>
-      <c r="E92" s="43"/>
-      <c r="F92" s="43"/>
-      <c r="G92" s="43"/>
-      <c r="H92" s="43"/>
-      <c r="I92" s="43"/>
-      <c r="J92" s="43"/>
-      <c r="K92" s="43"/>
-      <c r="L92" s="43"/>
-      <c r="M92" s="43"/>
-      <c r="N92" s="43"/>
+      <c r="A92" s="57"/>
+      <c r="B92" s="57"/>
+      <c r="C92" s="57"/>
+      <c r="D92" s="57"/>
+      <c r="E92" s="57"/>
+      <c r="F92" s="57"/>
+      <c r="G92" s="57"/>
+      <c r="H92" s="57"/>
+      <c r="I92" s="57"/>
+      <c r="J92" s="57"/>
+      <c r="K92" s="57"/>
+      <c r="L92" s="57"/>
+      <c r="M92" s="57"/>
+      <c r="N92" s="57"/>
       <c r="O92" s="5"/>
     </row>
     <row r="93" spans="1:15" s="6" customFormat="1" ht="15" customHeight="1">
-      <c r="A93" s="33"/>
-      <c r="B93" s="33"/>
-      <c r="C93" s="33"/>
-      <c r="D93" s="33"/>
-      <c r="E93" s="33"/>
-      <c r="F93" s="33"/>
-      <c r="G93" s="33"/>
-      <c r="H93" s="33"/>
-      <c r="I93" s="33"/>
-      <c r="J93" s="33"/>
-      <c r="K93" s="33"/>
-      <c r="L93" s="33"/>
-      <c r="M93" s="33"/>
-      <c r="N93" s="33"/>
+      <c r="A93" s="58"/>
+      <c r="B93" s="58"/>
+      <c r="C93" s="58"/>
+      <c r="D93" s="58"/>
+      <c r="E93" s="58"/>
+      <c r="F93" s="58"/>
+      <c r="G93" s="58"/>
+      <c r="H93" s="58"/>
+      <c r="I93" s="58"/>
+      <c r="J93" s="58"/>
+      <c r="K93" s="58"/>
+      <c r="L93" s="58"/>
+      <c r="M93" s="58"/>
+      <c r="N93" s="58"/>
       <c r="O93" s="5"/>
     </row>
     <row r="94" spans="1:15" s="6" customFormat="1" ht="15" customHeight="1">
-      <c r="A94" s="41"/>
-      <c r="B94" s="41"/>
-      <c r="C94" s="41"/>
-      <c r="D94" s="41"/>
-      <c r="E94" s="41"/>
-      <c r="F94" s="41"/>
-      <c r="G94" s="41"/>
-      <c r="H94" s="41"/>
-      <c r="I94" s="41"/>
-      <c r="J94" s="41"/>
-      <c r="K94" s="41"/>
-      <c r="L94" s="41"/>
-      <c r="M94" s="41"/>
-      <c r="N94" s="41"/>
+      <c r="A94" s="55"/>
+      <c r="B94" s="55"/>
+      <c r="C94" s="55"/>
+      <c r="D94" s="55"/>
+      <c r="E94" s="55"/>
+      <c r="F94" s="55"/>
+      <c r="G94" s="55"/>
+      <c r="H94" s="55"/>
+      <c r="I94" s="55"/>
+      <c r="J94" s="55"/>
+      <c r="K94" s="55"/>
+      <c r="L94" s="55"/>
+      <c r="M94" s="55"/>
+      <c r="N94" s="55"/>
       <c r="O94" s="5"/>
     </row>
     <row r="95" spans="1:15" s="6" customFormat="1" ht="15" customHeight="1">
       <c r="A95" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B95" s="42"/>
-      <c r="C95" s="42"/>
-      <c r="D95" s="42"/>
-      <c r="E95" s="42"/>
-      <c r="F95" s="42">
+        <v>8</v>
+      </c>
+      <c r="B95" s="56"/>
+      <c r="C95" s="56"/>
+      <c r="D95" s="56"/>
+      <c r="E95" s="56"/>
+      <c r="F95" s="56">
         <v>20</v>
       </c>
-      <c r="G95" s="42"/>
-      <c r="H95" s="37"/>
-      <c r="I95" s="37"/>
-      <c r="J95" s="37"/>
-      <c r="K95" s="37"/>
-      <c r="L95" s="37"/>
-      <c r="M95" s="37"/>
-      <c r="N95" s="37"/>
+      <c r="G95" s="56"/>
+      <c r="H95" s="47"/>
+      <c r="I95" s="47"/>
+      <c r="J95" s="47"/>
+      <c r="K95" s="47"/>
+      <c r="L95" s="47"/>
+      <c r="M95" s="47"/>
+      <c r="N95" s="47"/>
       <c r="O95" s="5"/>
     </row>
     <row r="96" spans="1:15" s="6" customFormat="1" ht="15" customHeight="1" thickBot="1">
       <c r="A96" s="7"/>
-      <c r="B96" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="C96" s="39"/>
-      <c r="D96" s="39"/>
-      <c r="E96" s="39"/>
-      <c r="F96" s="38"/>
-      <c r="G96" s="38"/>
-      <c r="H96" s="40" t="s">
-        <v>6</v>
-      </c>
-      <c r="I96" s="40"/>
-      <c r="J96" s="40"/>
+      <c r="B96" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="53"/>
+      <c r="D96" s="53"/>
+      <c r="E96" s="53"/>
+      <c r="F96" s="52"/>
+      <c r="G96" s="52"/>
+      <c r="H96" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="54"/>
+      <c r="J96" s="54"/>
       <c r="K96" s="30"/>
       <c r="L96" s="30"/>
       <c r="M96" s="30"/>
@@ -2568,63 +2568,148 @@
       <c r="O96" s="5"/>
     </row>
     <row r="97" spans="1:14">
-      <c r="A97" s="37"/>
-      <c r="B97" s="37"/>
-      <c r="C97" s="37"/>
-      <c r="D97" s="37"/>
-      <c r="E97" s="37"/>
-      <c r="F97" s="37"/>
-      <c r="G97" s="37"/>
-      <c r="H97" s="37"/>
-      <c r="I97" s="37"/>
-      <c r="J97" s="37"/>
-      <c r="K97" s="37"/>
-      <c r="L97" s="37"/>
-      <c r="M97" s="37"/>
-      <c r="N97" s="37"/>
+      <c r="A97" s="47"/>
+      <c r="B97" s="47"/>
+      <c r="C97" s="47"/>
+      <c r="D97" s="47"/>
+      <c r="E97" s="47"/>
+      <c r="F97" s="47"/>
+      <c r="G97" s="47"/>
+      <c r="H97" s="47"/>
+      <c r="I97" s="47"/>
+      <c r="J97" s="47"/>
+      <c r="K97" s="47"/>
+      <c r="L97" s="47"/>
+      <c r="M97" s="47"/>
+      <c r="N97" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="197">
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="J32:L32"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="A28:N28"/>
-    <mergeCell ref="J30:L30"/>
-    <mergeCell ref="J29:L29"/>
-    <mergeCell ref="K55:N55"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="A42:N42"/>
-    <mergeCell ref="A44:N44"/>
-    <mergeCell ref="A45:N45"/>
-    <mergeCell ref="A46:N46"/>
-    <mergeCell ref="K53:N53"/>
-    <mergeCell ref="K54:N54"/>
-    <mergeCell ref="K50:N50"/>
-    <mergeCell ref="K52:N52"/>
-    <mergeCell ref="A41:N41"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="J27:L27"/>
-    <mergeCell ref="J26:L26"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="F15:N15"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="H12:N12"/>
-    <mergeCell ref="F17:N17"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="G48:J48"/>
+    <mergeCell ref="G49:J49"/>
+    <mergeCell ref="G50:J50"/>
+    <mergeCell ref="G51:J51"/>
+    <mergeCell ref="G52:J52"/>
+    <mergeCell ref="G53:J53"/>
+    <mergeCell ref="G54:J54"/>
+    <mergeCell ref="G55:J55"/>
+    <mergeCell ref="G56:J56"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="A38:N38"/>
+    <mergeCell ref="A40:N40"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="A39:N39"/>
+    <mergeCell ref="A37:N37"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="J31:L31"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="K49:N49"/>
+    <mergeCell ref="A58:N58"/>
+    <mergeCell ref="K56:N56"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="F72:N72"/>
+    <mergeCell ref="J71:L71"/>
+    <mergeCell ref="M71:N71"/>
+    <mergeCell ref="A85:N85"/>
+    <mergeCell ref="A67:N67"/>
+    <mergeCell ref="A79:N79"/>
+    <mergeCell ref="A83:N83"/>
+    <mergeCell ref="A70:N70"/>
+    <mergeCell ref="A82:N82"/>
+    <mergeCell ref="A84:N84"/>
+    <mergeCell ref="A73:N73"/>
+    <mergeCell ref="A81:N81"/>
+    <mergeCell ref="A76:N76"/>
+    <mergeCell ref="A80:N80"/>
+    <mergeCell ref="A75:N75"/>
+    <mergeCell ref="A77:N77"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A97:N97"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="H96:J96"/>
+    <mergeCell ref="K96:N96"/>
+    <mergeCell ref="A89:N89"/>
+    <mergeCell ref="A94:N94"/>
+    <mergeCell ref="B95:E95"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="H95:N95"/>
+    <mergeCell ref="A92:N92"/>
+    <mergeCell ref="A90:N90"/>
+    <mergeCell ref="A91:N91"/>
+    <mergeCell ref="A86:N86"/>
+    <mergeCell ref="A93:N93"/>
+    <mergeCell ref="A87:N87"/>
+    <mergeCell ref="A88:N88"/>
+    <mergeCell ref="A63:N63"/>
+    <mergeCell ref="A78:N78"/>
+    <mergeCell ref="A74:N74"/>
+    <mergeCell ref="A68:N68"/>
+    <mergeCell ref="A66:N66"/>
+    <mergeCell ref="A69:N69"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A60:N60"/>
+    <mergeCell ref="A61:N61"/>
+    <mergeCell ref="A13:N13"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="F19:N19"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="F16:N16"/>
+    <mergeCell ref="J25:L25"/>
+    <mergeCell ref="J24:L24"/>
+    <mergeCell ref="A22:N22"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A43:N43"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="F20:N20"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="H23:I23"/>
@@ -2649,139 +2734,54 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:J2"/>
     <mergeCell ref="C9:J9"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A60:N60"/>
-    <mergeCell ref="A61:N61"/>
-    <mergeCell ref="A13:N13"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="F19:N19"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="F16:N16"/>
-    <mergeCell ref="J25:L25"/>
-    <mergeCell ref="J24:L24"/>
-    <mergeCell ref="A22:N22"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A43:N43"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A97:N97"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="H96:J96"/>
-    <mergeCell ref="K96:N96"/>
-    <mergeCell ref="A89:N89"/>
-    <mergeCell ref="A94:N94"/>
-    <mergeCell ref="B95:E95"/>
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="H95:N95"/>
-    <mergeCell ref="A92:N92"/>
-    <mergeCell ref="A90:N90"/>
-    <mergeCell ref="A91:N91"/>
-    <mergeCell ref="A86:N86"/>
-    <mergeCell ref="A93:N93"/>
-    <mergeCell ref="A87:N87"/>
-    <mergeCell ref="A88:N88"/>
-    <mergeCell ref="A63:N63"/>
-    <mergeCell ref="A78:N78"/>
-    <mergeCell ref="A74:N74"/>
-    <mergeCell ref="A68:N68"/>
-    <mergeCell ref="A66:N66"/>
-    <mergeCell ref="A69:N69"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="A28:N28"/>
+    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="J29:L29"/>
+    <mergeCell ref="K55:N55"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="A42:N42"/>
+    <mergeCell ref="A44:N44"/>
+    <mergeCell ref="A45:N45"/>
+    <mergeCell ref="A46:N46"/>
+    <mergeCell ref="K53:N53"/>
+    <mergeCell ref="K54:N54"/>
+    <mergeCell ref="K50:N50"/>
+    <mergeCell ref="K52:N52"/>
+    <mergeCell ref="A41:N41"/>
     <mergeCell ref="A65:N65"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="F72:N72"/>
-    <mergeCell ref="J71:L71"/>
-    <mergeCell ref="M71:N71"/>
-    <mergeCell ref="A85:N85"/>
-    <mergeCell ref="A67:N67"/>
-    <mergeCell ref="A79:N79"/>
-    <mergeCell ref="A83:N83"/>
-    <mergeCell ref="A70:N70"/>
-    <mergeCell ref="A82:N82"/>
-    <mergeCell ref="A84:N84"/>
-    <mergeCell ref="A73:N73"/>
     <mergeCell ref="A62:N62"/>
     <mergeCell ref="A59:N59"/>
     <mergeCell ref="A47:N47"/>
     <mergeCell ref="A57:N57"/>
     <mergeCell ref="A64:N64"/>
-    <mergeCell ref="A81:N81"/>
-    <mergeCell ref="A76:N76"/>
-    <mergeCell ref="A80:N80"/>
-    <mergeCell ref="A75:N75"/>
-    <mergeCell ref="A77:N77"/>
     <mergeCell ref="K51:N51"/>
     <mergeCell ref="K48:N48"/>
-    <mergeCell ref="K49:N49"/>
-    <mergeCell ref="A58:N58"/>
-    <mergeCell ref="K56:N56"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="A38:N38"/>
-    <mergeCell ref="A40:N40"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="A39:N39"/>
-    <mergeCell ref="A37:N37"/>
-    <mergeCell ref="J33:L33"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="J31:L31"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="E31:G31"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="G48:J48"/>
-    <mergeCell ref="G49:J49"/>
-    <mergeCell ref="G50:J50"/>
-    <mergeCell ref="G51:J51"/>
-    <mergeCell ref="G52:J52"/>
-    <mergeCell ref="G53:J53"/>
-    <mergeCell ref="G54:J54"/>
-    <mergeCell ref="G55:J55"/>
-    <mergeCell ref="G56:J56"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="J26:L26"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="F15:N15"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="H12:N12"/>
+    <mergeCell ref="F17:N17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.78740157480314965" right="0.39370078740157483" top="0.78740157480314965" bottom="0.78740157480314965" header="0" footer="0.19685039370078741"/>
